--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="91">
   <si>
     <t>Brand</t>
   </si>
@@ -88,18 +88,15 @@
     <t>360 degree cleaning brush</t>
   </si>
   <si>
+    <t>KIDS Socks</t>
+  </si>
+  <si>
     <t>WOMANS Boat Socks</t>
   </si>
   <si>
-    <t>KIDS Socks</t>
-  </si>
-  <si>
     <t>MANS Boat Socks 3 pairs</t>
   </si>
   <si>
-    <t>Household Utensils</t>
-  </si>
-  <si>
     <t>Foam Insole</t>
   </si>
   <si>
@@ -115,39 +112,30 @@
     <t>MANS No-show Socks</t>
   </si>
   <si>
+    <t>CL Roam Hands Free Traine</t>
+  </si>
+  <si>
     <t>low rise wOMANS socks 3 p</t>
   </si>
   <si>
     <t>WOMANS Low-cut Socks</t>
   </si>
   <si>
-    <t>CL Roam Hands Free Traine</t>
-  </si>
-  <si>
-    <t>DZL-Shoe Deodorization Bo</t>
-  </si>
-  <si>
     <t>6971340016867</t>
   </si>
   <si>
+    <t>6957352843639</t>
+  </si>
+  <si>
     <t>6957352859289</t>
   </si>
   <si>
-    <t>6957352843639</t>
-  </si>
-  <si>
     <t>6957352859265</t>
   </si>
   <si>
     <t>6957352859357</t>
   </si>
   <si>
-    <t>6957352859661</t>
-  </si>
-  <si>
-    <t>6957352859678</t>
-  </si>
-  <si>
     <t>6957352875425</t>
   </si>
   <si>
@@ -172,6 +160,12 @@
     <t>6957352803244</t>
   </si>
   <si>
+    <t>DS0771040840</t>
+  </si>
+  <si>
+    <t>6957352843691</t>
+  </si>
+  <si>
     <t>6957352859258</t>
   </si>
   <si>
@@ -181,39 +175,24 @@
     <t>6957352789913</t>
   </si>
   <si>
-    <t>6957352843691</t>
-  </si>
-  <si>
-    <t>DS0771040840</t>
-  </si>
-  <si>
-    <t>6957352858961</t>
-  </si>
-  <si>
     <t>6957352859333</t>
   </si>
   <si>
     <t>720976</t>
   </si>
   <si>
+    <t>720922</t>
+  </si>
+  <si>
     <t>720944</t>
   </si>
   <si>
-    <t>720922</t>
-  </si>
-  <si>
     <t>720951</t>
   </si>
   <si>
     <t>720933</t>
   </si>
   <si>
-    <t>720966</t>
-  </si>
-  <si>
-    <t>720960</t>
-  </si>
-  <si>
     <t>731029</t>
   </si>
   <si>
@@ -238,6 +217,12 @@
     <t>720868</t>
   </si>
   <si>
+    <t>726186</t>
+  </si>
+  <si>
+    <t>720918</t>
+  </si>
+  <si>
     <t>730709</t>
   </si>
   <si>
@@ -247,36 +232,21 @@
     <t>720808</t>
   </si>
   <si>
-    <t>720918</t>
-  </si>
-  <si>
-    <t>726186</t>
-  </si>
-  <si>
-    <t>730692</t>
-  </si>
-  <si>
     <t>720935</t>
   </si>
   <si>
     <t xml:space="preserve">360 degree cleaning brush UNISEX 0 </t>
   </si>
   <si>
+    <t>DZL Childrens Low-cut Socks # 16-18</t>
+  </si>
+  <si>
     <t>DZL-5A Antibacterial and Anti pilli</t>
   </si>
   <si>
-    <t>DZL Childrens Low-cut Socks # 16-18</t>
-  </si>
-  <si>
     <t>DZL-5A Antibacterial Foot Loop Wome</t>
   </si>
   <si>
-    <t>DZL-Vacuum Cup # green -600ML</t>
-  </si>
-  <si>
-    <t>DZL-Vacuum Cup # white -600ML</t>
-  </si>
-  <si>
     <t>Foam Insole UNISEX Beige Accessorie</t>
   </si>
   <si>
@@ -292,6 +262,12 @@
     <t>DZL Mens No-show Socks-Black#2015</t>
   </si>
   <si>
+    <t>CL Roam Hands Free Trainer MAN Blac</t>
+  </si>
+  <si>
+    <t>DZL Childrens Low-cut Socks # 18-20</t>
+  </si>
+  <si>
     <t>DZL-5A antibacterial and anti pilli</t>
   </si>
   <si>
@@ -301,19 +277,10 @@
     <t>DZL Ladys Low-cut Socks-Black</t>
   </si>
   <si>
-    <t>DZL Childrens Low-cut Socks # 18-20</t>
-  </si>
-  <si>
-    <t>CL Roam Hands Free Trainer MAN Blac</t>
-  </si>
-  <si>
-    <t>DZL-Shoe Deodorization Box UNISEX O</t>
-  </si>
-  <si>
     <t>Accessories</t>
   </si>
   <si>
-    <t>Footwear (Shoes)</t>
+    <t>Shoes</t>
   </si>
   <si>
     <t>Central Warehouse (KSWH - Limited: 1)</t>
@@ -651,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -718,16 +685,16 @@
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -745,7 +712,7 @@
         <v>19</v>
       </c>
       <c r="O2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -765,16 +732,16 @@
         <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -792,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="O3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -812,16 +779,16 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -839,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="O4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -859,16 +826,16 @@
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -886,7 +853,7 @@
         <v>8</v>
       </c>
       <c r="O5" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -906,16 +873,16 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -933,7 +900,7 @@
         <v>8</v>
       </c>
       <c r="O6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -950,19 +917,19 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -980,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -991,25 +958,25 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1024,10 +991,10 @@
         <v>3</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O8" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1044,19 +1011,19 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1074,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="O9" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1091,19 +1058,19 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1112,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10">
         <v>6</v>
       </c>
       <c r="O10" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1132,25 +1099,25 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1159,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>6</v>
       </c>
       <c r="O11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1185,19 +1152,19 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1215,7 +1182,7 @@
         <v>6</v>
       </c>
       <c r="O12" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1226,25 +1193,25 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1256,13 +1223,13 @@
         <v>0.2</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="O13" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1279,19 +1246,19 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1303,13 +1270,13 @@
         <v>0.2</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>6</v>
       </c>
       <c r="O14" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1326,19 +1293,19 @@
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1356,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="O15" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1373,19 +1340,19 @@
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1403,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -1414,25 +1381,25 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1450,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="O17" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -1467,19 +1434,19 @@
         <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1491,13 +1458,13 @@
         <v>0.2</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>6</v>
       </c>
       <c r="O18" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -1508,43 +1475,43 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>0.2</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>6</v>
       </c>
       <c r="O19" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -1555,25 +1522,25 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
         <v>82</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1591,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="O20" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -1602,31 +1569,31 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" t="s">
         <v>73</v>
       </c>
-      <c r="H21" t="s">
-        <v>91</v>
-      </c>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>0.2</v>
@@ -1638,7 +1605,7 @@
         <v>6</v>
       </c>
       <c r="O21" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1649,25 +1616,25 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H22" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1685,7 +1652,7 @@
         <v>6</v>
       </c>
       <c r="O22" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -1702,19 +1669,19 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H23" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1732,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="O23" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -1749,19 +1716,19 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H24" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1779,7 +1746,7 @@
         <v>6</v>
       </c>
       <c r="O24" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -1790,25 +1757,25 @@
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H25" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1826,7 +1793,7 @@
         <v>6</v>
       </c>
       <c r="O25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -1837,25 +1804,25 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H26" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1864,16 +1831,16 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>6</v>
       </c>
       <c r="O26" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -1884,25 +1851,25 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H27" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1920,7 +1887,7 @@
         <v>6</v>
       </c>
       <c r="O27" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -1931,25 +1898,25 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G28" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1967,148 +1934,7 @@
         <v>6</v>
       </c>
       <c r="O28" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29" t="s">
-        <v>78</v>
-      </c>
-      <c r="H29" t="s">
-        <v>96</v>
-      </c>
-      <c r="I29" t="s">
-        <v>99</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>0.1</v>
-      </c>
-      <c r="M29">
-        <v>7</v>
-      </c>
-      <c r="N29">
-        <v>6</v>
-      </c>
-      <c r="O29" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" t="s">
-        <v>79</v>
-      </c>
-      <c r="H30" t="s">
-        <v>97</v>
-      </c>
-      <c r="I30" t="s">
-        <v>98</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>0.1</v>
-      </c>
-      <c r="M30">
-        <v>7</v>
-      </c>
-      <c r="N30">
-        <v>6</v>
-      </c>
-      <c r="O30" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31" t="s">
-        <v>80</v>
-      </c>
-      <c r="H31" t="s">
-        <v>90</v>
-      </c>
-      <c r="I31" t="s">
-        <v>98</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>0.1</v>
-      </c>
-      <c r="M31">
-        <v>7</v>
-      </c>
-      <c r="N31">
-        <v>6</v>
-      </c>
-      <c r="O31" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="94">
   <si>
     <t>Brand</t>
   </si>
@@ -139,15 +139,15 @@
     <t>6957352875425</t>
   </si>
   <si>
+    <t>6957352859036</t>
+  </si>
+  <si>
+    <t>6957352859340</t>
+  </si>
+  <si>
     <t>6957352859272</t>
   </si>
   <si>
-    <t>6957352859036</t>
-  </si>
-  <si>
-    <t>6957352859340</t>
-  </si>
-  <si>
     <t>6971277830871</t>
   </si>
   <si>
@@ -166,6 +166,9 @@
     <t>6957352843691</t>
   </si>
   <si>
+    <t>6957352859333</t>
+  </si>
+  <si>
     <t>6957352859258</t>
   </si>
   <si>
@@ -175,7 +178,7 @@
     <t>6957352789913</t>
   </si>
   <si>
-    <t>6957352859333</t>
+    <t>6957352875371</t>
   </si>
   <si>
     <t>720976</t>
@@ -196,15 +199,15 @@
     <t>731029</t>
   </si>
   <si>
+    <t>720939</t>
+  </si>
+  <si>
+    <t>720957</t>
+  </si>
+  <si>
     <t>720953</t>
   </si>
   <si>
-    <t>720939</t>
-  </si>
-  <si>
-    <t>720957</t>
-  </si>
-  <si>
     <t>720978</t>
   </si>
   <si>
@@ -223,6 +226,9 @@
     <t>720918</t>
   </si>
   <si>
+    <t>720935</t>
+  </si>
+  <si>
     <t>730709</t>
   </si>
   <si>
@@ -232,7 +238,7 @@
     <t>720808</t>
   </si>
   <si>
-    <t>720935</t>
+    <t>731017</t>
   </si>
   <si>
     <t xml:space="preserve">360 degree cleaning brush UNISEX 0 </t>
@@ -275,6 +281,9 @@
   </si>
   <si>
     <t>DZL Ladys Low-cut Socks-Black</t>
+  </si>
+  <si>
+    <t>Foam Insole UNISEX Black Accessorie</t>
   </si>
   <si>
     <t>Accessories</t>
@@ -618,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -688,13 +697,13 @@
         <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -703,16 +712,16 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -735,13 +744,13 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -759,7 +768,7 @@
         <v>9</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -782,13 +791,13 @@
         <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -806,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="O4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -817,10 +826,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
@@ -829,13 +838,13 @@
         <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -853,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="O5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -864,10 +873,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
@@ -876,13 +885,13 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -900,7 +909,7 @@
         <v>8</v>
       </c>
       <c r="O6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -923,13 +932,13 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -947,7 +956,7 @@
         <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -958,25 +967,25 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -994,7 +1003,7 @@
         <v>6</v>
       </c>
       <c r="O8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1005,25 +1014,25 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1041,7 +1050,7 @@
         <v>6</v>
       </c>
       <c r="O9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1052,25 +1061,25 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
         <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1088,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="O10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1099,25 +1108,25 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s">
         <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1135,7 +1144,7 @@
         <v>6</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1152,19 +1161,19 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
         <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1182,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="O12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1193,25 +1202,25 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1223,13 +1232,13 @@
         <v>0.2</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="O13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1240,25 +1249,25 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1276,7 +1285,7 @@
         <v>6</v>
       </c>
       <c r="O14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1299,13 +1308,13 @@
         <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1323,7 +1332,7 @@
         <v>6</v>
       </c>
       <c r="O15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -1334,10 +1343,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
@@ -1346,13 +1355,13 @@
         <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1370,7 +1379,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -1381,25 +1390,25 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1417,7 +1426,7 @@
         <v>6</v>
       </c>
       <c r="O17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -1440,13 +1449,13 @@
         <v>46</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1464,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="O18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -1487,13 +1496,13 @@
         <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1511,7 +1520,7 @@
         <v>6</v>
       </c>
       <c r="O19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -1534,13 +1543,13 @@
         <v>48</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -1558,7 +1567,7 @@
         <v>6</v>
       </c>
       <c r="O20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -1581,13 +1590,13 @@
         <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -1605,7 +1614,7 @@
         <v>6</v>
       </c>
       <c r="O21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1628,13 +1637,13 @@
         <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -1652,7 +1661,7 @@
         <v>6</v>
       </c>
       <c r="O22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -1669,19 +1678,19 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
         <v>50</v>
       </c>
       <c r="G23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1699,7 +1708,7 @@
         <v>6</v>
       </c>
       <c r="O23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -1716,19 +1725,19 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1746,7 +1755,7 @@
         <v>6</v>
       </c>
       <c r="O24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -1763,19 +1772,19 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>52</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -1793,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="O25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -1804,25 +1813,25 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -1831,16 +1840,16 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="M26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>6</v>
       </c>
       <c r="O26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -1851,25 +1860,25 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G27" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -1887,7 +1896,7 @@
         <v>6</v>
       </c>
       <c r="O27" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -1898,25 +1907,25 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H28" t="s">
         <v>80</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -1934,7 +1943,54 @@
         <v>6</v>
       </c>
       <c r="O28" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>0.1</v>
+      </c>
+      <c r="M29">
+        <v>7</v>
+      </c>
+      <c r="N29">
+        <v>6</v>
+      </c>
+      <c r="O29" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -73,7 +73,7 @@
     <t>2 - Routine (Accessory)</t>
   </si>
   <si>
-    <t>Predictive WH Replenishment</t>
+    <t>Store Transfer (IST - Peer Network)</t>
   </si>
   <si>
     <t>K111</t>
@@ -856,10 +856,10 @@
     <t>⚠️ Stock-Out in 7d (Vel: 0.1/d)</t>
   </si>
   <si>
-    <t>Central Warehouse (KSWH - Limited: 1)</t>
-  </si>
-  <si>
-    <t>Central Warehouse (KSWH - Limited: 0)</t>
+    <t>Peer Store Network (WH Stock: 1 - Cross-Store Balance)</t>
+  </si>
+  <si>
+    <t>Peer Store Network (WH Stock: 0 - Cross-Store Balance)</t>
   </si>
 </sst>
 </file>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -73,7 +73,7 @@
     <t>2 - Routine (Accessory)</t>
   </si>
   <si>
-    <t>Store Transfer (IST - Peer Network)</t>
+    <t>Predictive WH Replenishment</t>
   </si>
   <si>
     <t>K111</t>
@@ -856,10 +856,10 @@
     <t>⚠️ Stock-Out in 7d (Vel: 0.1/d)</t>
   </si>
   <si>
-    <t>Peer Store Network (WH Stock: 1 - Cross-Store Balance)</t>
-  </si>
-  <si>
-    <t>Peer Store Network (WH Stock: 0 - Cross-Store Balance)</t>
+    <t>Central Warehouse (KSWH - Limited: 1)</t>
+  </si>
+  <si>
+    <t>Central Warehouse (KSWH - Limited: 0)</t>
   </si>
 </sst>
 </file>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -73,7 +73,7 @@
     <t>2 - Routine (Accessory)</t>
   </si>
   <si>
-    <t>Store Transfer (IST - Peer Network)</t>
+    <t>Store Transfer (IST - Network Balancing)</t>
   </si>
   <si>
     <t>K111</t>
@@ -856,10 +856,10 @@
     <t>⚠️ Stock-Out in 7d (Vel: 0.1/d)</t>
   </si>
   <si>
-    <t>Peer Store Network (WH Stock: 1 - Cross-Store Balance)</t>
-  </si>
-  <si>
-    <t>Peer Store Network (WH Stock: 0 - Cross-Store Balance)</t>
+    <t>Peer Store Network (WH Stock: 1 - Cross-Store Balancing)</t>
+  </si>
+  <si>
+    <t>Peer Store Network (WH Stock: 0 - Cross-Store Balancing)</t>
   </si>
 </sst>
 </file>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="286">
   <si>
     <t>Brand</t>
   </si>
@@ -133,15 +133,15 @@
     <t>MANS Boat Socks 3 pairs</t>
   </si>
   <si>
+    <t>Cleaning Wipes</t>
+  </si>
+  <si>
     <t>Foam Insole</t>
   </si>
   <si>
     <t>Shoe Cleaning Set (NEW)</t>
   </si>
   <si>
-    <t>Cleaning Wipes</t>
-  </si>
-  <si>
     <t>WOMANS Low-cut Socks</t>
   </si>
   <si>
@@ -199,6 +199,9 @@
     <t>DS0771062042</t>
   </si>
   <si>
+    <t>DD0471081541</t>
+  </si>
+  <si>
     <t>DB0101056543</t>
   </si>
   <si>
@@ -283,6 +286,9 @@
     <t>DS0844069527</t>
   </si>
   <si>
+    <t>DS0846069646</t>
+  </si>
+  <si>
     <t>DB0102056538</t>
   </si>
   <si>
@@ -325,7 +331,7 @@
     <t>DB0106069547</t>
   </si>
   <si>
-    <t>DD0471081541</t>
+    <t>DD0591072141</t>
   </si>
   <si>
     <t>DD0592042237</t>
@@ -382,6 +388,9 @@
     <t>6957352859357</t>
   </si>
   <si>
+    <t>6957352859036</t>
+  </si>
+  <si>
     <t>6957352875425</t>
   </si>
   <si>
@@ -394,9 +403,6 @@
     <t>6971277830871</t>
   </si>
   <si>
-    <t>6957352859036</t>
-  </si>
-  <si>
     <t>6957352859326</t>
   </si>
   <si>
@@ -469,6 +475,9 @@
     <t>726133</t>
   </si>
   <si>
+    <t>726175</t>
+  </si>
+  <si>
     <t>726571</t>
   </si>
   <si>
@@ -553,6 +562,9 @@
     <t>726803</t>
   </si>
   <si>
+    <t>726850</t>
+  </si>
+  <si>
     <t>726590</t>
   </si>
   <si>
@@ -595,7 +607,7 @@
     <t>726630</t>
   </si>
   <si>
-    <t>726175</t>
+    <t>726672</t>
   </si>
   <si>
     <t>726675</t>
@@ -652,6 +664,9 @@
     <t>720933</t>
   </si>
   <si>
+    <t>720939</t>
+  </si>
+  <si>
     <t>731029</t>
   </si>
   <si>
@@ -664,9 +679,6 @@
     <t>720978</t>
   </si>
   <si>
-    <t>720939</t>
-  </si>
-  <si>
     <t>720949</t>
   </si>
   <si>
@@ -718,12 +730,12 @@
     <t>CL Streak Nylon Trainer MAN Pale Be</t>
   </si>
   <si>
+    <t>BR Crossway Nylon Runner Sneaker MA</t>
+  </si>
+  <si>
     <t>SI Rove Synthetic Suede Sneaker MAN</t>
   </si>
   <si>
-    <t>BR Crossway Nylon Runner Sneaker MA</t>
-  </si>
-  <si>
     <t xml:space="preserve">BR Ripple Nylon Runner Sneaker MAN </t>
   </si>
   <si>
@@ -796,13 +808,13 @@
     <t>DZL-5A Antibacterial Foot Loop Wome</t>
   </si>
   <si>
+    <t>Cleaning Wipes UNISEX 0 Care Produc</t>
+  </si>
+  <si>
     <t>Foam Insole UNISEX Beige Accessorie</t>
   </si>
   <si>
     <t>Shoe Cleaning Set (NEW) UNISEX 0 Ca</t>
-  </si>
-  <si>
-    <t>Cleaning Wipes UNISEX 0 Care Produc</t>
   </si>
   <si>
     <t>DZL-5A Antibacterial Foot Loop Mens</t>
@@ -1191,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P124"/>
+  <dimension ref="A1:P128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1267,13 +1279,13 @@
         <v>46</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1285,13 +1297,13 @@
         <v>0.2</v>
       </c>
       <c r="N2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O2">
         <v>6</v>
       </c>
       <c r="P2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1317,13 +1329,13 @@
         <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1335,13 +1347,13 @@
         <v>0.1</v>
       </c>
       <c r="N3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O3">
         <v>6</v>
       </c>
       <c r="P3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1367,13 +1379,13 @@
         <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1385,13 +1397,13 @@
         <v>0.1</v>
       </c>
       <c r="N4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O4">
         <v>6</v>
       </c>
       <c r="P4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1417,13 +1429,13 @@
         <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1435,13 +1447,13 @@
         <v>0.1</v>
       </c>
       <c r="N5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1467,13 +1479,13 @@
         <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I6" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1485,13 +1497,13 @@
         <v>0.1</v>
       </c>
       <c r="N6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1517,13 +1529,13 @@
         <v>51</v>
       </c>
       <c r="H7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I7" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1535,13 +1547,13 @@
         <v>0.1</v>
       </c>
       <c r="N7" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1567,13 +1579,13 @@
         <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I8" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1585,13 +1597,13 @@
         <v>0.1</v>
       </c>
       <c r="N8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O8">
         <v>6</v>
       </c>
       <c r="P8" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1617,13 +1629,13 @@
         <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1635,13 +1647,13 @@
         <v>0.1</v>
       </c>
       <c r="N9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1667,13 +1679,13 @@
         <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1685,13 +1697,13 @@
         <v>0.1</v>
       </c>
       <c r="N10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O10">
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1717,13 +1729,13 @@
         <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J11" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1735,13 +1747,13 @@
         <v>0.1</v>
       </c>
       <c r="N11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O11">
         <v>6</v>
       </c>
       <c r="P11" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1767,13 +1779,13 @@
         <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1785,13 +1797,13 @@
         <v>0.1</v>
       </c>
       <c r="N12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1817,13 +1829,13 @@
         <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I13" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J13" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1835,13 +1847,13 @@
         <v>0.1</v>
       </c>
       <c r="N13" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O13">
         <v>6</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1867,13 +1879,13 @@
         <v>56</v>
       </c>
       <c r="H14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I14" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J14" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1885,13 +1897,13 @@
         <v>0.1</v>
       </c>
       <c r="N14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O14">
         <v>6</v>
       </c>
       <c r="P14" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1917,13 +1929,13 @@
         <v>57</v>
       </c>
       <c r="H15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I15" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1935,13 +1947,13 @@
         <v>0.1</v>
       </c>
       <c r="N15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1967,13 +1979,13 @@
         <v>58</v>
       </c>
       <c r="H16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I16" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J16" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1985,13 +1997,13 @@
         <v>0.1</v>
       </c>
       <c r="N16" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O16">
         <v>6</v>
       </c>
       <c r="P16" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2017,13 +2029,13 @@
         <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I17" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J17" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -2035,13 +2047,13 @@
         <v>0.1</v>
       </c>
       <c r="N17" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O17">
         <v>6</v>
       </c>
       <c r="P17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2067,13 +2079,13 @@
         <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I18" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J18" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2085,13 +2097,13 @@
         <v>0.1</v>
       </c>
       <c r="N18" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O18">
         <v>6</v>
       </c>
       <c r="P18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2111,37 +2123,37 @@
         <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="J19" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>0.1</v>
       </c>
       <c r="N19" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O19">
         <v>6</v>
       </c>
       <c r="P19" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2164,16 +2176,16 @@
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H20" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I20" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J20" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2185,13 +2197,13 @@
         <v>0.1</v>
       </c>
       <c r="N20" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O20">
         <v>6</v>
       </c>
       <c r="P20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2214,16 +2226,16 @@
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J21" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2235,13 +2247,13 @@
         <v>0.1</v>
       </c>
       <c r="N21" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2255,25 +2267,25 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J22" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2282,16 +2294,16 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N22" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O22">
         <v>6</v>
       </c>
       <c r="P22" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2317,13 +2329,13 @@
         <v>62</v>
       </c>
       <c r="H23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I23" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J23" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2335,13 +2347,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O23">
         <v>6</v>
       </c>
       <c r="P23" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2367,13 +2379,13 @@
         <v>63</v>
       </c>
       <c r="H24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I24" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="J24" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2385,13 +2397,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2417,13 +2429,13 @@
         <v>64</v>
       </c>
       <c r="H25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I25" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J25" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2435,13 +2447,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O25">
         <v>6</v>
       </c>
       <c r="P25" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2467,13 +2479,13 @@
         <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I26" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J26" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2485,13 +2497,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O26">
         <v>6</v>
       </c>
       <c r="P26" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2511,37 +2523,37 @@
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G27" t="s">
         <v>66</v>
       </c>
       <c r="H27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J27" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2561,19 +2573,19 @@
         <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
         <v>67</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I28" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J28" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2585,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O28">
         <v>6</v>
       </c>
       <c r="P28" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2611,37 +2623,37 @@
         <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H29" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="I29" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="J29" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2664,16 +2676,16 @@
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="H30" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="I30" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J30" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2685,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O30">
         <v>6</v>
       </c>
       <c r="P30" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2717,31 +2729,31 @@
         <v>69</v>
       </c>
       <c r="H31" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J31" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O31">
         <v>6</v>
       </c>
       <c r="P31" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2767,31 +2779,31 @@
         <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I32" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J32" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2817,13 +2829,13 @@
         <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I33" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J33" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -2835,13 +2847,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O33">
         <v>6</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2867,13 +2879,13 @@
         <v>72</v>
       </c>
       <c r="H34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I34" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="J34" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -2885,13 +2897,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2914,16 +2926,16 @@
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H35" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="I35" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J35" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2935,13 +2947,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
       <c r="P35" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2964,16 +2976,16 @@
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="I36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J36" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -2985,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O36">
         <v>6</v>
       </c>
       <c r="P36" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3017,13 +3029,13 @@
         <v>74</v>
       </c>
       <c r="H37" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I37" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J37" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3035,13 +3047,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O37">
         <v>6</v>
       </c>
       <c r="P37" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3067,13 +3079,13 @@
         <v>75</v>
       </c>
       <c r="H38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J38" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3085,13 +3097,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O38">
         <v>6</v>
       </c>
       <c r="P38" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3117,13 +3129,13 @@
         <v>76</v>
       </c>
       <c r="H39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="J39" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -3135,13 +3147,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O39">
         <v>6</v>
       </c>
       <c r="P39" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3161,37 +3173,37 @@
         <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G40" t="s">
         <v>77</v>
       </c>
       <c r="H40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J40" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3217,13 +3229,13 @@
         <v>78</v>
       </c>
       <c r="H41" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I41" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="J41" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3235,13 +3247,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O41">
         <v>6</v>
       </c>
       <c r="P41" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3261,37 +3273,37 @@
         <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G42" t="s">
         <v>79</v>
       </c>
       <c r="H42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I42" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="J42" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42">
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O42">
         <v>6</v>
       </c>
       <c r="P42" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3311,19 +3323,19 @@
         <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
         <v>80</v>
       </c>
       <c r="H43" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I43" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J43" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -3335,13 +3347,13 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O43">
         <v>6</v>
       </c>
       <c r="P43" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3367,31 +3379,31 @@
         <v>81</v>
       </c>
       <c r="H44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I44" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J44" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K44">
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O44">
         <v>6</v>
       </c>
       <c r="P44" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3417,13 +3429,13 @@
         <v>82</v>
       </c>
       <c r="H45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I45" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J45" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -3435,13 +3447,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O45">
         <v>6</v>
       </c>
       <c r="P45" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3467,13 +3479,13 @@
         <v>83</v>
       </c>
       <c r="H46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I46" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J46" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -3485,13 +3497,13 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O46">
         <v>6</v>
       </c>
       <c r="P46" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3511,19 +3523,19 @@
         <v>24</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G47" t="s">
         <v>84</v>
       </c>
       <c r="H47" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J47" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -3535,13 +3547,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O47">
         <v>6</v>
       </c>
       <c r="P47" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3567,13 +3579,13 @@
         <v>85</v>
       </c>
       <c r="H48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I48" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J48" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -3585,13 +3597,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O48">
         <v>6</v>
       </c>
       <c r="P48" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3617,31 +3629,31 @@
         <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I49" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J49" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K49">
         <v>1</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O49">
         <v>6</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3667,13 +3679,13 @@
         <v>87</v>
       </c>
       <c r="H50" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I50" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J50" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -3685,13 +3697,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O50">
         <v>6</v>
       </c>
       <c r="P50" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3717,13 +3729,13 @@
         <v>88</v>
       </c>
       <c r="H51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="J51" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K51">
         <v>1</v>
@@ -3735,13 +3747,13 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O51">
         <v>6</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3755,25 +3767,25 @@
         <v>19</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F52" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G52" t="s">
         <v>89</v>
       </c>
       <c r="H52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I52" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="J52" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -3785,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O52">
         <v>6</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3805,43 +3817,43 @@
         <v>19</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F53" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G53" t="s">
         <v>90</v>
       </c>
       <c r="H53" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I53" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="J53" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O53">
         <v>6</v>
       </c>
       <c r="P53" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3861,19 +3873,19 @@
         <v>23</v>
       </c>
       <c r="F54" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G54" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="I54" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J54" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -3885,13 +3897,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O54">
         <v>6</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3911,37 +3923,37 @@
         <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="I55" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J55" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K55">
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O55">
         <v>6</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3964,16 +3976,16 @@
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J56" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K56">
         <v>1</v>
@@ -3985,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O56">
         <v>6</v>
       </c>
       <c r="P56" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4014,16 +4026,16 @@
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H57" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I57" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J57" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -4035,13 +4047,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O57">
         <v>6</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4064,16 +4076,16 @@
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H58" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I58" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J58" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K58">
         <v>1</v>
@@ -4085,13 +4097,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O58">
         <v>6</v>
       </c>
       <c r="P58" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4111,19 +4123,19 @@
         <v>23</v>
       </c>
       <c r="F59" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="H59" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="I59" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="J59" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K59">
         <v>1</v>
@@ -4135,13 +4147,13 @@
         <v>0</v>
       </c>
       <c r="N59" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O59">
         <v>6</v>
       </c>
       <c r="P59" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4161,19 +4173,19 @@
         <v>23</v>
       </c>
       <c r="F60" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I60" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="J60" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K60">
         <v>1</v>
@@ -4185,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O60">
         <v>6</v>
       </c>
       <c r="P60" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4214,16 +4226,16 @@
         <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="I61" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="J61" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K61">
         <v>1</v>
@@ -4235,13 +4247,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O61">
         <v>6</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4264,16 +4276,16 @@
         <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="I62" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="J62" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -4285,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O62">
         <v>6</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4314,16 +4326,16 @@
         <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H63" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="I63" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="J63" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K63">
         <v>1</v>
@@ -4335,13 +4347,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O63">
         <v>6</v>
       </c>
       <c r="P63" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4364,16 +4376,16 @@
         <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="I64" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J64" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K64">
         <v>1</v>
@@ -4385,13 +4397,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O64">
         <v>6</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4411,19 +4423,19 @@
         <v>23</v>
       </c>
       <c r="F65" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G65" t="s">
         <v>95</v>
       </c>
       <c r="H65" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I65" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J65" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K65">
         <v>1</v>
@@ -4435,13 +4447,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O65">
         <v>6</v>
       </c>
       <c r="P65" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4461,19 +4473,19 @@
         <v>23</v>
       </c>
       <c r="F66" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
         <v>96</v>
       </c>
       <c r="H66" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I66" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J66" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K66">
         <v>1</v>
@@ -4485,13 +4497,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O66">
         <v>6</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4517,13 +4529,13 @@
         <v>97</v>
       </c>
       <c r="H67" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I67" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J67" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K67">
         <v>1</v>
@@ -4535,13 +4547,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O67">
         <v>6</v>
       </c>
       <c r="P67" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4555,25 +4567,25 @@
         <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G68" t="s">
         <v>98</v>
       </c>
       <c r="H68" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I68" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="J68" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -4585,13 +4597,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O68">
         <v>6</v>
       </c>
       <c r="P68" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4605,25 +4617,25 @@
         <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G69" t="s">
         <v>99</v>
       </c>
       <c r="H69" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I69" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="J69" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K69">
         <v>1</v>
@@ -4635,13 +4647,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -4667,13 +4679,13 @@
         <v>100</v>
       </c>
       <c r="H70" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I70" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J70" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K70">
         <v>1</v>
@@ -4685,13 +4697,13 @@
         <v>0</v>
       </c>
       <c r="N70" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O70">
         <v>6</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -4714,16 +4726,16 @@
         <v>29</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H71" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I71" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J71" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -4735,13 +4747,13 @@
         <v>0</v>
       </c>
       <c r="N71" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O71">
         <v>6</v>
       </c>
       <c r="P71" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4764,16 +4776,16 @@
         <v>29</v>
       </c>
       <c r="G72" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="H72" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="I72" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J72" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K72">
         <v>1</v>
@@ -4785,13 +4797,13 @@
         <v>0</v>
       </c>
       <c r="N72" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O72">
         <v>6</v>
       </c>
       <c r="P72" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4814,16 +4826,16 @@
         <v>29</v>
       </c>
       <c r="G73" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I73" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J73" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K73">
         <v>1</v>
@@ -4835,13 +4847,13 @@
         <v>0</v>
       </c>
       <c r="N73" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O73">
         <v>6</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4864,16 +4876,16 @@
         <v>29</v>
       </c>
       <c r="G74" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="H74" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="I74" t="s">
         <v>234</v>
       </c>
       <c r="J74" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -4885,13 +4897,13 @@
         <v>0</v>
       </c>
       <c r="N74" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O74">
         <v>6</v>
       </c>
       <c r="P74" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4911,37 +4923,37 @@
         <v>25</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G75" t="s">
         <v>103</v>
       </c>
       <c r="H75" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I75" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J75" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K75">
         <v>1</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75">
         <v>0</v>
       </c>
       <c r="N75" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O75">
         <v>6</v>
       </c>
       <c r="P75" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4961,37 +4973,37 @@
         <v>25</v>
       </c>
       <c r="F76" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="H76" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="I76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J76" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76">
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O76">
         <v>6</v>
       </c>
       <c r="P76" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5011,19 +5023,19 @@
         <v>25</v>
       </c>
       <c r="F77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G77" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="H77" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="I77" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="J77" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -5035,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O77">
         <v>6</v>
       </c>
       <c r="P77" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5061,37 +5073,37 @@
         <v>25</v>
       </c>
       <c r="F78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H78" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="I78" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J78" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K78">
         <v>1</v>
       </c>
       <c r="L78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78">
         <v>0</v>
       </c>
       <c r="N78" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O78">
         <v>6</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5111,37 +5123,37 @@
         <v>25</v>
       </c>
       <c r="F79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="H79" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="I79" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J79" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K79">
         <v>1</v>
       </c>
       <c r="L79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79">
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O79">
         <v>6</v>
       </c>
       <c r="P79" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5161,37 +5173,37 @@
         <v>25</v>
       </c>
       <c r="F80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G80" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H80" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="I80" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J80" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K80">
         <v>1</v>
       </c>
       <c r="L80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80">
         <v>0</v>
       </c>
       <c r="N80" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O80">
         <v>6</v>
       </c>
       <c r="P80" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5214,16 +5226,16 @@
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H81" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="I81" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J81" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K81">
         <v>1</v>
@@ -5235,13 +5247,13 @@
         <v>0</v>
       </c>
       <c r="N81" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O81">
         <v>6</v>
       </c>
       <c r="P81" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5264,16 +5276,16 @@
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H82" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I82" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J82" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -5285,13 +5297,13 @@
         <v>0</v>
       </c>
       <c r="N82" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O82">
         <v>6</v>
       </c>
       <c r="P82" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5314,16 +5326,16 @@
         <v>26</v>
       </c>
       <c r="G83" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="H83" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="I83" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J83" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K83">
         <v>1</v>
@@ -5335,13 +5347,13 @@
         <v>0</v>
       </c>
       <c r="N83" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O83">
         <v>6</v>
       </c>
       <c r="P83" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5364,16 +5376,16 @@
         <v>26</v>
       </c>
       <c r="G84" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="H84" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="I84" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J84" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K84">
         <v>1</v>
@@ -5385,13 +5397,13 @@
         <v>0</v>
       </c>
       <c r="N84" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O84">
         <v>6</v>
       </c>
       <c r="P84" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5414,16 +5426,16 @@
         <v>26</v>
       </c>
       <c r="G85" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="I85" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="J85" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K85">
         <v>1</v>
@@ -5435,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="N85" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O85">
         <v>6</v>
       </c>
       <c r="P85" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5461,19 +5473,19 @@
         <v>25</v>
       </c>
       <c r="F86" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G86" t="s">
         <v>107</v>
       </c>
       <c r="H86" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I86" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="J86" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K86">
         <v>1</v>
@@ -5485,13 +5497,13 @@
         <v>0</v>
       </c>
       <c r="N86" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O86">
         <v>6</v>
       </c>
       <c r="P86" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5511,19 +5523,19 @@
         <v>25</v>
       </c>
       <c r="F87" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G87" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="H87" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="I87" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J87" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K87">
         <v>1</v>
@@ -5535,13 +5547,13 @@
         <v>0</v>
       </c>
       <c r="N87" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O87">
         <v>6</v>
       </c>
       <c r="P87" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5561,37 +5573,37 @@
         <v>25</v>
       </c>
       <c r="F88" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G88" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="H88" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="I88" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="J88" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88">
         <v>0</v>
       </c>
       <c r="N88" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O88">
         <v>6</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5611,37 +5623,37 @@
         <v>25</v>
       </c>
       <c r="F89" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G89" t="s">
         <v>109</v>
       </c>
       <c r="H89" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I89" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J89" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K89">
         <v>1</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89">
         <v>0</v>
       </c>
       <c r="N89" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O89">
         <v>6</v>
       </c>
       <c r="P89" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5661,37 +5673,37 @@
         <v>25</v>
       </c>
       <c r="F90" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G90" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="H90" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I90" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="J90" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90">
         <v>0</v>
       </c>
       <c r="N90" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O90">
         <v>6</v>
       </c>
       <c r="P90" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5711,37 +5723,37 @@
         <v>25</v>
       </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I91" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="J91" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K91">
         <v>1</v>
       </c>
       <c r="L91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91">
         <v>0</v>
       </c>
       <c r="N91" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O91">
         <v>6</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5761,37 +5773,37 @@
         <v>25</v>
       </c>
       <c r="F92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G92" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I92" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="J92" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K92">
         <v>1</v>
       </c>
       <c r="L92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92">
         <v>0</v>
       </c>
       <c r="N92" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O92">
         <v>6</v>
       </c>
       <c r="P92" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5811,37 +5823,37 @@
         <v>25</v>
       </c>
       <c r="F93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I93" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="J93" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K93">
         <v>1</v>
       </c>
       <c r="L93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93">
         <v>0</v>
       </c>
       <c r="N93" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O93">
         <v>6</v>
       </c>
       <c r="P93" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5861,37 +5873,37 @@
         <v>25</v>
       </c>
       <c r="F94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G94" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="H94" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="I94" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J94" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K94">
         <v>1</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94">
         <v>0</v>
       </c>
       <c r="N94" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O94">
         <v>6</v>
       </c>
       <c r="P94" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5917,13 +5929,13 @@
         <v>114</v>
       </c>
       <c r="H95" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I95" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="J95" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K95">
         <v>1</v>
@@ -5935,13 +5947,13 @@
         <v>0</v>
       </c>
       <c r="N95" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O95">
         <v>6</v>
       </c>
       <c r="P95" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5967,31 +5979,31 @@
         <v>115</v>
       </c>
       <c r="H96" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I96" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="J96" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K96">
         <v>1</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96">
         <v>0</v>
       </c>
       <c r="N96" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O96">
         <v>6</v>
       </c>
       <c r="P96" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6014,34 +6026,34 @@
         <v>33</v>
       </c>
       <c r="G97" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="I97" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="J97" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K97">
         <v>1</v>
       </c>
       <c r="L97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97">
         <v>0</v>
       </c>
       <c r="N97" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O97">
         <v>6</v>
       </c>
       <c r="P97" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6049,31 +6061,31 @@
         <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C98" t="s">
         <v>19</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G98" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H98" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I98" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J98" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K98">
         <v>1</v>
@@ -6082,16 +6094,16 @@
         <v>1</v>
       </c>
       <c r="M98">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N98" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O98">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="P98" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6099,49 +6111,49 @@
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C99" t="s">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E99" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F99" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G99" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I99" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J99" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O99">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P99" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6149,31 +6161,31 @@
         <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C100" t="s">
         <v>19</v>
       </c>
       <c r="D100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F100" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H100" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I100" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J100" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K100">
         <v>1</v>
@@ -6182,16 +6194,16 @@
         <v>1</v>
       </c>
       <c r="M100">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N100" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O100">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P100" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6211,19 +6223,19 @@
         <v>24</v>
       </c>
       <c r="F101" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I101" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J101" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K101">
         <v>1</v>
@@ -6232,16 +6244,16 @@
         <v>1</v>
       </c>
       <c r="M101">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="N101" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O101">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6255,25 +6267,25 @@
         <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F102" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G102" t="s">
         <v>120</v>
       </c>
       <c r="H102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I102" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J102" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K102">
         <v>1</v>
@@ -6282,16 +6294,16 @@
         <v>1</v>
       </c>
       <c r="M102">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N102" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O102">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P102" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6305,10 +6317,10 @@
         <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F103" t="s">
         <v>37</v>
@@ -6317,13 +6329,13 @@
         <v>121</v>
       </c>
       <c r="H103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I103" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J103" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K103">
         <v>1</v>
@@ -6332,16 +6344,16 @@
         <v>1</v>
       </c>
       <c r="M103">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N103" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O103">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P103" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6355,25 +6367,25 @@
         <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E104" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G104" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H104" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I104" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J104" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K104">
         <v>1</v>
@@ -6382,16 +6394,16 @@
         <v>1</v>
       </c>
       <c r="M104">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N104" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O104">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P104" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6405,25 +6417,25 @@
         <v>19</v>
       </c>
       <c r="D105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G105" t="s">
         <v>122</v>
       </c>
       <c r="H105" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I105" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J105" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K105">
         <v>1</v>
@@ -6435,13 +6447,13 @@
         <v>0.3</v>
       </c>
       <c r="N105" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="O105">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P105" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6455,25 +6467,25 @@
         <v>19</v>
       </c>
       <c r="D106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E106" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G106" t="s">
         <v>123</v>
       </c>
       <c r="H106" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I106" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J106" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K106">
         <v>1</v>
@@ -6482,16 +6494,16 @@
         <v>1</v>
       </c>
       <c r="M106">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N106" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P106" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6505,25 +6517,25 @@
         <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G107" t="s">
         <v>124</v>
       </c>
       <c r="H107" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J107" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K107">
         <v>1</v>
@@ -6532,16 +6544,16 @@
         <v>1</v>
       </c>
       <c r="M107">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N107" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="O107">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P107" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6555,25 +6567,25 @@
         <v>19</v>
       </c>
       <c r="D108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F108" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G108" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H108" t="s">
         <v>215</v>
       </c>
       <c r="I108" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J108" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K108">
         <v>1</v>
@@ -6582,16 +6594,16 @@
         <v>1</v>
       </c>
       <c r="M108">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N108" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="O108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P108" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6605,25 +6617,25 @@
         <v>19</v>
       </c>
       <c r="D109" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F109" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I109" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J109" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K109">
         <v>1</v>
@@ -6632,16 +6644,16 @@
         <v>1</v>
       </c>
       <c r="M109">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N109" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="O109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P109" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -6661,19 +6673,19 @@
         <v>24</v>
       </c>
       <c r="F110" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G110" t="s">
         <v>126</v>
       </c>
       <c r="H110" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I110" t="s">
         <v>262</v>
       </c>
       <c r="J110" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K110">
         <v>1</v>
@@ -6685,13 +6697,13 @@
         <v>0.2</v>
       </c>
       <c r="N110" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P110" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -6711,19 +6723,19 @@
         <v>24</v>
       </c>
       <c r="F111" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G111" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H111" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="I111" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J111" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K111">
         <v>1</v>
@@ -6735,13 +6747,13 @@
         <v>0.2</v>
       </c>
       <c r="N111" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P111" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -6761,19 +6773,19 @@
         <v>23</v>
       </c>
       <c r="F112" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G112" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H112" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I112" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J112" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K112">
         <v>1</v>
@@ -6785,13 +6797,13 @@
         <v>0.2</v>
       </c>
       <c r="N112" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O112">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P112" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6805,25 +6817,25 @@
         <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F113" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G113" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H113" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I113" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="J113" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K113">
         <v>1</v>
@@ -6835,13 +6847,13 @@
         <v>0.2</v>
       </c>
       <c r="N113" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="O113">
         <v>4</v>
       </c>
       <c r="P113" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6861,19 +6873,19 @@
         <v>24</v>
       </c>
       <c r="F114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G114" t="s">
         <v>128</v>
       </c>
       <c r="H114" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I114" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J114" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K114">
         <v>1</v>
@@ -6885,13 +6897,13 @@
         <v>0.2</v>
       </c>
       <c r="N114" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O114">
         <v>4</v>
       </c>
       <c r="P114" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6905,25 +6917,25 @@
         <v>19</v>
       </c>
       <c r="D115" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G115" t="s">
         <v>129</v>
       </c>
       <c r="H115" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I115" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J115" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K115">
         <v>1</v>
@@ -6935,13 +6947,13 @@
         <v>0.2</v>
       </c>
       <c r="N115" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O115">
         <v>4</v>
       </c>
       <c r="P115" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6955,25 +6967,25 @@
         <v>19</v>
       </c>
       <c r="D116" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F116" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G116" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H116" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="I116" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J116" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K116">
         <v>1</v>
@@ -6985,13 +6997,13 @@
         <v>0.2</v>
       </c>
       <c r="N116" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O116">
         <v>4</v>
       </c>
       <c r="P116" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7005,25 +7017,25 @@
         <v>19</v>
       </c>
       <c r="D117" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E117" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G117" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H117" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I117" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J117" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K117">
         <v>1</v>
@@ -7035,13 +7047,13 @@
         <v>0.2</v>
       </c>
       <c r="N117" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O117">
         <v>4</v>
       </c>
       <c r="P117" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7055,25 +7067,25 @@
         <v>19</v>
       </c>
       <c r="D118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F118" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G118" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H118" t="s">
         <v>222</v>
       </c>
       <c r="I118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J118" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K118">
         <v>1</v>
@@ -7085,13 +7097,13 @@
         <v>0.2</v>
       </c>
       <c r="N118" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O118">
         <v>4</v>
       </c>
       <c r="P118" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7105,25 +7117,25 @@
         <v>19</v>
       </c>
       <c r="D119" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F119" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G119" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H119" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="I119" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J119" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -7135,13 +7147,13 @@
         <v>0.2</v>
       </c>
       <c r="N119" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O119">
         <v>4</v>
       </c>
       <c r="P119" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7155,43 +7167,43 @@
         <v>19</v>
       </c>
       <c r="D120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F120" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G120" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H120" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I120" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J120" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K120">
         <v>1</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120">
         <v>0.2</v>
       </c>
       <c r="N120" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O120">
         <v>4</v>
       </c>
       <c r="P120" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7205,25 +7217,25 @@
         <v>19</v>
       </c>
       <c r="D121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F121" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I121" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="J121" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K121">
         <v>1</v>
@@ -7235,13 +7247,13 @@
         <v>0.2</v>
       </c>
       <c r="N121" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O121">
         <v>4</v>
       </c>
       <c r="P121" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7255,25 +7267,25 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E122" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F122" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G122" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H122" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I122" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J122" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K122">
         <v>1</v>
@@ -7282,16 +7294,16 @@
         <v>1</v>
       </c>
       <c r="M122">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N122" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O122">
         <v>4</v>
       </c>
       <c r="P122" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7305,43 +7317,43 @@
         <v>19</v>
       </c>
       <c r="D123" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E123" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G123" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H123" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="I123" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="J123" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N123" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O123">
         <v>4</v>
       </c>
       <c r="P123" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7361,19 +7373,19 @@
         <v>25</v>
       </c>
       <c r="F124" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G124" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="H124" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="I124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J124" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K124">
         <v>1</v>
@@ -7382,16 +7394,216 @@
         <v>1</v>
       </c>
       <c r="M124">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N124" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="O124">
         <v>4</v>
       </c>
       <c r="P124" t="s">
-        <v>280</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125" t="s">
+        <v>16</v>
+      </c>
+      <c r="B125" t="s">
+        <v>18</v>
+      </c>
+      <c r="C125" t="s">
+        <v>19</v>
+      </c>
+      <c r="D125" t="s">
+        <v>21</v>
+      </c>
+      <c r="E125" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" t="s">
+        <v>40</v>
+      </c>
+      <c r="G125" t="s">
+        <v>137</v>
+      </c>
+      <c r="H125" t="s">
+        <v>229</v>
+      </c>
+      <c r="I125" t="s">
+        <v>273</v>
+      </c>
+      <c r="J125" t="s">
+        <v>275</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <v>0.1</v>
+      </c>
+      <c r="N125" t="s">
+        <v>283</v>
+      </c>
+      <c r="O125">
+        <v>4</v>
+      </c>
+      <c r="P125" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126" t="s">
+        <v>16</v>
+      </c>
+      <c r="B126" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" t="s">
+        <v>19</v>
+      </c>
+      <c r="D126" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" t="s">
+        <v>23</v>
+      </c>
+      <c r="F126" t="s">
+        <v>39</v>
+      </c>
+      <c r="G126" t="s">
+        <v>124</v>
+      </c>
+      <c r="H126" t="s">
+        <v>216</v>
+      </c>
+      <c r="I126" t="s">
+        <v>264</v>
+      </c>
+      <c r="J126" t="s">
+        <v>275</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>0.1</v>
+      </c>
+      <c r="N126" t="s">
+        <v>283</v>
+      </c>
+      <c r="O126">
+        <v>4</v>
+      </c>
+      <c r="P126" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127" t="s">
+        <v>16</v>
+      </c>
+      <c r="B127" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" t="s">
+        <v>19</v>
+      </c>
+      <c r="D127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127" t="s">
+        <v>37</v>
+      </c>
+      <c r="G127" t="s">
+        <v>127</v>
+      </c>
+      <c r="H127" t="s">
+        <v>219</v>
+      </c>
+      <c r="I127" t="s">
+        <v>263</v>
+      </c>
+      <c r="J127" t="s">
+        <v>275</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <v>0.1</v>
+      </c>
+      <c r="N127" t="s">
+        <v>283</v>
+      </c>
+      <c r="O127">
+        <v>4</v>
+      </c>
+      <c r="P127" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128" t="s">
+        <v>16</v>
+      </c>
+      <c r="B128" t="s">
+        <v>18</v>
+      </c>
+      <c r="C128" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" t="s">
+        <v>22</v>
+      </c>
+      <c r="E128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" t="s">
+        <v>37</v>
+      </c>
+      <c r="G128" t="s">
+        <v>127</v>
+      </c>
+      <c r="H128" t="s">
+        <v>219</v>
+      </c>
+      <c r="I128" t="s">
+        <v>263</v>
+      </c>
+      <c r="J128" t="s">
+        <v>275</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>0.1</v>
+      </c>
+      <c r="N128" t="s">
+        <v>283</v>
+      </c>
+      <c r="O128">
+        <v>4</v>
+      </c>
+      <c r="P128" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="72">
   <si>
     <t>Brand</t>
   </si>
@@ -40,9 +40,42 @@
     <t>DZL</t>
   </si>
   <si>
+    <t>DZL Riyadh U-Walk</t>
+  </si>
+  <si>
     <t>DZL Riyadh Park</t>
   </si>
   <si>
+    <t>725536</t>
+  </si>
+  <si>
+    <t>725570</t>
+  </si>
+  <si>
+    <t>725678</t>
+  </si>
+  <si>
+    <t>725879</t>
+  </si>
+  <si>
+    <t>726672</t>
+  </si>
+  <si>
+    <t>730127</t>
+  </si>
+  <si>
+    <t>794027</t>
+  </si>
+  <si>
+    <t>794041</t>
+  </si>
+  <si>
+    <t>800131</t>
+  </si>
+  <si>
+    <t>810013</t>
+  </si>
+  <si>
     <t>720969</t>
   </si>
   <si>
@@ -103,19 +136,34 @@
     <t>726806</t>
   </si>
   <si>
-    <t>729571</t>
-  </si>
-  <si>
-    <t>794015</t>
-  </si>
-  <si>
-    <t>794016</t>
-  </si>
-  <si>
-    <t>794018</t>
-  </si>
-  <si>
-    <t>794020</t>
+    <t>CL Wander Trainer MAN White 40</t>
+  </si>
+  <si>
+    <t>CL Wander Trainer WOMAN White 38</t>
+  </si>
+  <si>
+    <t>CL Highland Sock Trainer WOMAN White 38</t>
+  </si>
+  <si>
+    <t>CL Canyon Wool Trainer PS Fog Grey/Light Grey 26</t>
+  </si>
+  <si>
+    <t>BR Ripple Nylon Runner Sneaker MAN Black/Dark Grey 41</t>
+  </si>
+  <si>
+    <t>AQ Three-Strap SS Sandal WOMAN Cocoa 38</t>
+  </si>
+  <si>
+    <t>BR-Nexus-Knit-Runner-Sneaker-MAN-Black-44</t>
+  </si>
+  <si>
+    <t>BR-Nexus-Knit-Runner-Sneaker-MAN-Black-43</t>
+  </si>
+  <si>
+    <t>CL Ripple Wool TrainerCreamMEN</t>
+  </si>
+  <si>
+    <t>CL WANDER TRAINER WOMAN WHITE 36.5</t>
   </si>
   <si>
     <t>DZL-SHOE DEODORIZER SPRAY#150ML UNISEX 0 Care Products0UNISEX</t>
@@ -178,22 +226,7 @@
     <t>CL Classic SS Trainer KIDS Black 26</t>
   </si>
   <si>
-    <t>BR Ripple Runner Sneaker MAN Black/Grey 40</t>
-  </si>
-  <si>
-    <t>BR-Nexus-Knit-Runner-Sneaker-MAN-Black-40</t>
-  </si>
-  <si>
-    <t>BR-Nexus-Knit-Runner-Sneaker-MAN-Pale-Beige-45</t>
-  </si>
-  <si>
-    <t>BR-Nexus-Knit-Runner-Sneaker-MAN-Pale-Beige-41</t>
-  </si>
-  <si>
-    <t>BR-Nexus-Knit-Runner-Sneaker-MAN-Pale-Beige-44</t>
-  </si>
-  <si>
-    <t>DZL Riyadh U-Walk</t>
+    <t>DZL Solitaire</t>
   </si>
   <si>
     <t>🏙️ Same City</t>
@@ -528,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -562,19 +595,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -585,19 +618,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -608,19 +641,19 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -631,19 +664,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -654,19 +687,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -677,19 +710,19 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -700,19 +733,19 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -723,19 +756,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -746,19 +779,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -769,19 +802,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -789,22 +822,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -812,22 +845,22 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -835,22 +868,22 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -858,22 +891,22 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -881,22 +914,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -904,22 +937,22 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -927,22 +960,22 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -950,22 +983,22 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F19">
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -973,22 +1006,22 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -996,22 +1029,22 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1019,22 +1052,22 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F22">
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1042,22 +1075,22 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1065,22 +1098,22 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F24">
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1088,22 +1121,22 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F25">
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1111,22 +1144,137 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -226,10 +226,10 @@
     <t>CL Classic SS Trainer KIDS Black 26</t>
   </si>
   <si>
-    <t>DZL Solitaire</t>
-  </si>
-  <si>
-    <t>🏙️ Same City</t>
+    <t>DZL Redsea</t>
+  </si>
+  <si>
+    <t>🚛 Inter-City</t>
   </si>
 </sst>
 </file>

--- a/Reports/Auto_Replenishment_DZL.xlsx
+++ b/Reports/Auto_Replenishment_DZL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="73">
   <si>
     <t>Brand</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>DZL Redsea</t>
+  </si>
+  <si>
+    <t>🏙️ Same City</t>
   </si>
   <si>
     <t>🚛 Inter-City</t>
@@ -601,7 +604,7 @@
         <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -624,7 +627,7 @@
         <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -647,7 +650,7 @@
         <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -670,7 +673,7 @@
         <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -693,7 +696,7 @@
         <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -716,7 +719,7 @@
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -739,7 +742,7 @@
         <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -762,7 +765,7 @@
         <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -785,7 +788,7 @@
         <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -808,7 +811,7 @@
         <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -837,7 +840,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -860,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -883,7 +886,7 @@
         <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -906,7 +909,7 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -929,7 +932,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -952,7 +955,7 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -975,7 +978,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -998,7 +1001,7 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1021,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1044,7 +1047,7 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1067,7 +1070,7 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1090,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1113,7 +1116,7 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1136,7 +1139,7 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1159,7 +1162,7 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1182,7 +1185,7 @@
         <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1205,7 +1208,7 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1228,7 +1231,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1251,7 +1254,7 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1274,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
